--- a/Projects/Datasets for Excel/Datasets for excel/advanced+filtering+data.xlsx
+++ b/Projects/Datasets for Excel/Datasets for excel/advanced+filtering+data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shahriar/Desktop/PROJECTs/Course/Data - Excel/7. advanced filtering/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DS\tezendra\Projects\Datasets for Excel\Datasets for excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B85E619-6431-7F44-BFC0-47E580E7A1FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77852459-A447-454D-AB30-B01F50B5958F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{46B74526-A74E-6046-9D0E-2CEB55D79120}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="16520" xr2:uid="{46B74526-A74E-6046-9D0E-2CEB55D79120}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -228,9 +228,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -268,7 +268,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -374,7 +374,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -516,7 +516,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -524,21 +524,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D40BF641-9A5E-7143-93C1-2643454410EF}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="16.3" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -562,21 +563,21 @@
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B2">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>0</v>
@@ -594,21 +595,21 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B3">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
         <v>39</v>
@@ -617,7 +618,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -637,7 +638,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -654,7 +655,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -671,21 +672,21 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B7">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -693,7 +694,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -710,7 +711,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -727,24 +728,24 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B10">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -761,7 +762,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -778,7 +779,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -795,7 +796,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -812,7 +813,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>15</v>
       </c>
@@ -829,7 +830,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -846,7 +847,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>29</v>
       </c>
@@ -863,7 +864,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -880,7 +881,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -897,7 +898,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -914,7 +915,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -931,7 +932,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>15</v>
       </c>
@@ -948,7 +949,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -965,7 +966,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -982,7 +983,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -999,7 +1000,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>26</v>
       </c>
@@ -1016,7 +1017,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>13</v>
       </c>
@@ -1033,7 +1034,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>22</v>
       </c>
@@ -1050,7 +1051,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -1067,7 +1068,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>9</v>
       </c>
@@ -1084,7 +1085,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>35</v>
       </c>
@@ -1101,7 +1102,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>22</v>
       </c>
@@ -1118,7 +1119,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -1135,7 +1136,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>26</v>
       </c>
@@ -1152,7 +1153,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>13</v>
       </c>
@@ -1169,7 +1170,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>13</v>
       </c>
@@ -1186,7 +1187,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>35</v>
       </c>
@@ -1203,12 +1204,12 @@
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B38">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="C38" t="s">
         <v>16</v>
@@ -1217,10 +1218,10 @@
         <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>9</v>
       </c>
@@ -1237,7 +1238,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -1254,7 +1255,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>35</v>
       </c>
@@ -1271,24 +1272,24 @@
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B42">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C42" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D42" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E42" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>19</v>
       </c>
@@ -1305,7 +1306,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>22</v>
       </c>
@@ -1322,7 +1323,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>13</v>
       </c>
@@ -1339,7 +1340,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>9</v>
       </c>
@@ -1356,7 +1357,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>22</v>
       </c>
@@ -1373,7 +1374,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>5</v>
       </c>
@@ -1390,7 +1391,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>19</v>
       </c>
@@ -1407,7 +1408,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>13</v>
       </c>
@@ -1424,7 +1425,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>33</v>
       </c>
@@ -1442,6 +1443,9 @@
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E42">
+    <sortCondition ref="B1:B51"/>
+  </sortState>
   <mergeCells count="1">
     <mergeCell ref="G1:K1"/>
   </mergeCells>
